--- a/engineering_basics/dft/forward_dft.xlsx
+++ b/engineering_basics/dft/forward_dft.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="196">
   <si>
     <t xml:space="preserve">Line Num</t>
   </si>
@@ -2255,11 +2255,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="62616022"/>
-        <c:axId val="47407687"/>
+        <c:axId val="33574547"/>
+        <c:axId val="53458440"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="62616022"/>
+        <c:axId val="33574547"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2336,12 +2336,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="47407687"/>
+        <c:crossAx val="53458440"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="47407687"/>
+        <c:axId val="53458440"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2418,7 +2418,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="62616022"/>
+        <c:crossAx val="33574547"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2481,9 +2481,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>546840</xdr:colOff>
+      <xdr:colOff>546480</xdr:colOff>
       <xdr:row>36</xdr:row>
-      <xdr:rowOff>28080</xdr:rowOff>
+      <xdr:rowOff>27720</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2492,7 +2492,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="3963600" y="380160"/>
-        <a:ext cx="9778680" cy="5500080"/>
+        <a:ext cx="9778320" cy="5499720"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2616,7 +2616,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H77"/>
+  <dimension ref="A1:H78"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="14.65" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.53"/>
@@ -4560,13 +4560,13 @@
     </row>
     <row r="76" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="11" t="n">
-        <v>74</v>
-      </c>
-      <c r="B76" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="C76" s="21" t="s">
-        <v>130</v>
+        <v>75</v>
+      </c>
+      <c r="B76" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>174</v>
@@ -4581,17 +4581,43 @@
         <v>35</v>
       </c>
       <c r="H76" s="4" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="11" t="n">
+        <v>75</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C77" s="21" t="s">
+        <v>130</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H77" s="4" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="23"/>
-      <c r="B77" s="24"/>
-      <c r="C77" s="25"/>
-      <c r="D77" s="24"/>
-      <c r="E77" s="24"/>
-      <c r="F77" s="24"/>
-      <c r="G77" s="24"/>
+    <row r="78" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="23"/>
+      <c r="B78" s="24"/>
+      <c r="C78" s="25"/>
+      <c r="D78" s="24"/>
+      <c r="E78" s="24"/>
+      <c r="F78" s="24"/>
+      <c r="G78" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -4600,7 +4626,7 @@
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="D1:G1"/>
   </mergeCells>
-  <conditionalFormatting sqref="C1:C2 C4:C723">
+  <conditionalFormatting sqref="C1:C2 C4:C724">
     <cfRule type="containsText" priority="2" operator="containsText" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="uSTO C" dxfId="0">
       <formula>NOT(ISERROR(SEARCH("uSTO C",C1)))</formula>
     </cfRule>
@@ -4611,7 +4637,7 @@
       <formula>NOT(ISERROR(SEARCH("uSTO B",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C2 C4:C732">
+  <conditionalFormatting sqref="C1:C2 C4:C733">
     <cfRule type="containsText" priority="5" operator="containsText" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="uSTO A" dxfId="0">
       <formula>NOT(ISERROR(SEARCH("uSTO A",C1)))</formula>
     </cfRule>

--- a/engineering_basics/dft/forward_dft.xlsx
+++ b/engineering_basics/dft/forward_dft.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="206">
   <si>
     <t xml:space="preserve">Line Num</t>
   </si>
@@ -447,7 +447,34 @@
     <t xml:space="preserve">Main program Discrete Fourier Transform (Calculates all bins of a N point DFT) No input needed</t>
   </si>
   <si>
-    <t xml:space="preserve">Setup to make a 2xN matrix</t>
+    <t xml:space="preserve">Set size of B to [int((size A)/2) 2]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">col/2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43 44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">int(col/2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">int(col/2)+1</t>
   </si>
   <si>
     <t xml:space="preserve">34</t>
@@ -501,9 +528,6 @@
     <t xml:space="preserve">Increment k</t>
   </si>
   <si>
-    <t xml:space="preserve">+</t>
-  </si>
-  <si>
     <t xml:space="preserve">k+1</t>
   </si>
   <si>
@@ -532,6 +556,12 @@
   </si>
   <si>
     <t xml:space="preserve">STO 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45 23 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RCL DIM B</t>
   </si>
   <si>
     <t xml:space="preserve">k+1 </t>
@@ -641,7 +671,7 @@
     <numFmt numFmtId="167" formatCode="0.0"/>
     <numFmt numFmtId="168" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="30">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -825,6 +855,11 @@
       <name val="Courier New"/>
       <family val="3"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Courier New"/>
+      <family val="3"/>
     </font>
     <font>
       <sz val="13"/>
@@ -1317,7 +1352,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="47">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1395,6 +1430,14 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="23" fillId="4" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1681,19 +1724,17 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1300" spc="-1" strike="noStrike">
+              <a:defRPr b="0" sz="1300" strike="noStrike" u="none">
+                <a:uFillTx/>
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr b="0" sz="1300" strike="noStrike" u="none">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
-                <a:latin typeface="Arial"/>
-                <a:ea typeface="DejaVu Sans"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr b="0" sz="1300" spc="-1" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
+                <a:uFillTx/>
                 <a:latin typeface="Arial"/>
                 <a:ea typeface="DejaVu Sans"/>
               </a:rPr>
@@ -1749,10 +1790,11 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
+                    <a:uFillTx/>
                     <a:latin typeface="Arial"/>
                     <a:ea typeface="DejaVu Sans"/>
                   </a:defRPr>
@@ -1767,6 +1809,15 @@
             <c:showPercent val="0"/>
             <c:separator> </c:separator>
             <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="28800">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                </a:ln>
+              </c:spPr>
+            </c:leaderLines>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
@@ -1995,10 +2046,11 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
+                    <a:uFillTx/>
                     <a:latin typeface="Arial"/>
                     <a:ea typeface="DejaVu Sans"/>
                   </a:defRPr>
@@ -2013,6 +2065,15 @@
             <c:showPercent val="0"/>
             <c:separator> </c:separator>
             <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="28800">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                </a:ln>
+              </c:spPr>
+            </c:leaderLines>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
@@ -2255,11 +2316,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="33574547"/>
-        <c:axId val="53458440"/>
+        <c:axId val="9336723"/>
+        <c:axId val="58099746"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="33574547"/>
+        <c:axId val="9336723"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2281,19 +2342,17 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="900" spc="-1" strike="noStrike">
+                  <a:defRPr b="0" sz="1300" strike="noStrike" u="none">
+                    <a:uFillTx/>
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr b="0" sz="900" strike="noStrike" u="none">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
-                    <a:latin typeface="Arial"/>
-                    <a:ea typeface="DejaVu Sans"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr b="0" sz="900" spc="-1" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
+                    <a:uFillTx/>
                     <a:latin typeface="Arial"/>
                     <a:ea typeface="DejaVu Sans"/>
                   </a:rPr>
@@ -2326,22 +2385,23 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
+                <a:uFillTx/>
                 <a:latin typeface="Arial"/>
                 <a:ea typeface="DejaVu Sans"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="53458440"/>
+        <c:crossAx val="58099746"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="53458440"/>
+        <c:axId val="58099746"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2363,19 +2423,17 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="900" spc="-1" strike="noStrike">
+                  <a:defRPr b="0" sz="1300" strike="noStrike" u="none">
+                    <a:uFillTx/>
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr b="0" sz="900" strike="noStrike" u="none">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
-                    <a:latin typeface="Arial"/>
-                    <a:ea typeface="DejaVu Sans"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr b="0" sz="900" spc="-1" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
+                    <a:uFillTx/>
                     <a:latin typeface="Arial"/>
                     <a:ea typeface="DejaVu Sans"/>
                   </a:rPr>
@@ -2408,17 +2466,18 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
+                <a:uFillTx/>
                 <a:latin typeface="Arial"/>
                 <a:ea typeface="DejaVu Sans"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="33574547"/>
+        <c:crossAx val="9336723"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2445,10 +2504,11 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+            <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
+              <a:uFillTx/>
               <a:latin typeface="Arial"/>
               <a:ea typeface="DejaVu Sans"/>
             </a:defRPr>
@@ -2481,9 +2541,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>546480</xdr:colOff>
+      <xdr:colOff>545760</xdr:colOff>
       <xdr:row>36</xdr:row>
-      <xdr:rowOff>27720</xdr:rowOff>
+      <xdr:rowOff>27000</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2492,7 +2552,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="3963600" y="380160"/>
-        <a:ext cx="9778320" cy="5499720"/>
+        <a:ext cx="9777600" cy="5499000"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2616,8 +2676,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H78"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="14.65" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:H83"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="14.65" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.53"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="11.53"/>
@@ -3904,7 +3964,7 @@
       <c r="G50" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="H50" s="20" t="s">
+      <c r="H50" s="4" t="s">
         <v>135</v>
       </c>
     </row>
@@ -3919,13 +3979,13 @@
         <v>137</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E51" s="2" t="n">
-        <v>2</v>
+        <v>138</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>12</v>
@@ -3939,19 +3999,19 @@
         <v>50</v>
       </c>
       <c r="B52" s="12" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C52" s="15" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E52" s="2" t="n">
-        <v>2</v>
+        <v>141</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>12</v>
@@ -3965,155 +4025,155 @@
         <v>51</v>
       </c>
       <c r="B53" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="C53" s="3" t="n">
-        <v>0</v>
+        <v>84</v>
+      </c>
+      <c r="C53" s="15" t="n">
+        <v>1</v>
       </c>
       <c r="D53" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F53" s="2" t="n">
-        <v>2</v>
+        <v>141</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="H53" s="20" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="11" t="n">
         <v>52</v>
       </c>
-      <c r="B54" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C54" s="3" t="s">
+      <c r="B54" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="D54" s="2" t="n">
-        <v>0</v>
+      <c r="C54" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>144</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F54" s="2" t="n">
-        <v>2</v>
+        <v>35</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="H54" s="20" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="11" t="n">
         <v>53</v>
       </c>
-      <c r="B55" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C55" s="21" t="s">
+      <c r="B55" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="C55" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E55" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="D55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F55" s="2" t="n">
-        <v>2</v>
+      <c r="F55" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="H55" s="4" t="s">
-        <v>145</v>
+        <v>12</v>
+      </c>
+      <c r="H55" s="21" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="11" t="n">
         <v>54</v>
       </c>
-      <c r="B56" s="2" t="s">
+      <c r="B56" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="C56" s="15" t="s">
         <v>146</v>
       </c>
-      <c r="C56" s="3" t="s">
-        <v>147</v>
-      </c>
       <c r="D56" s="2" t="s">
-        <v>11</v>
+        <v>144</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="G56" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H56" s="4" t="s">
-        <v>148</v>
+        <v>35</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H56" s="21" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="11" t="n">
         <v>55</v>
       </c>
-      <c r="B57" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="C57" s="22" t="s">
-        <v>150</v>
+      <c r="B57" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="C57" s="15" t="s">
+        <v>148</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>127</v>
+        <v>144</v>
+      </c>
+      <c r="E57" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="H57" s="14" t="s">
-        <v>151</v>
+        <v>12</v>
+      </c>
+      <c r="H57" s="21" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="11" t="n">
         <v>56</v>
       </c>
-      <c r="B58" s="2" t="n">
-        <v>1</v>
+      <c r="B58" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="C58" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D58" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="F58" s="2" t="s">
-        <v>127</v>
+        <v>144</v>
+      </c>
+      <c r="F58" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="H58" s="4" t="s">
-        <v>152</v>
+        <v>35</v>
+      </c>
+      <c r="H58" s="22" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4121,51 +4181,51 @@
         <v>57</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E59" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F59" s="2" t="s">
-        <v>125</v>
+        <v>151</v>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F59" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="H59" s="4" t="s">
-        <v>152</v>
+        <v>35</v>
+      </c>
+      <c r="H59" s="22" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="11" t="n">
         <v>58</v>
       </c>
-      <c r="B60" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="C60" s="3" t="s">
+      <c r="B60" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C60" s="23" t="s">
         <v>153</v>
       </c>
-      <c r="D60" s="2" t="s">
+      <c r="D60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F60" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H60" s="4" t="s">
         <v>154</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="F60" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="G60" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="H60" s="4" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4173,25 +4233,25 @@
         <v>59</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>142</v>
+        <v>156</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>125</v>
+        <v>11</v>
+      </c>
+      <c r="E61" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="G61" s="2" t="s">
-        <v>127</v>
+        <v>34</v>
+      </c>
+      <c r="G61" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="H61" s="4" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4199,25 +4259,25 @@
         <v>60</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
+      </c>
+      <c r="C62" s="24" t="s">
+        <v>159</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>154</v>
+        <v>125</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>127</v>
+        <v>34</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="H62" s="4" t="s">
-        <v>158</v>
+        <v>34</v>
+      </c>
+      <c r="H62" s="14" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4225,25 +4285,25 @@
         <v>61</v>
       </c>
       <c r="B63" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="D63" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D63" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" s="2" t="s">
         <v>125</v>
-      </c>
-      <c r="E63" s="2" t="s">
-        <v>154</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>127</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>127</v>
+        <v>34</v>
       </c>
       <c r="H63" s="4" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4251,42 +4311,42 @@
         <v>62</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="D64" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E64" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F64" s="2" t="s">
         <v>125</v>
-      </c>
-      <c r="E64" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="F64" s="2" t="s">
-        <v>127</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>127</v>
       </c>
       <c r="H64" s="4" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="11" t="n">
         <v>63</v>
       </c>
-      <c r="B65" s="2" t="s">
-        <v>56</v>
+      <c r="B65" s="2" t="n">
+        <v>40</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>57</v>
+        <v>143</v>
       </c>
       <c r="D65" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="E65" s="2" t="s">
         <v>125</v>
-      </c>
-      <c r="E65" s="2" t="s">
-        <v>154</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>127</v>
@@ -4295,33 +4355,33 @@
         <v>127</v>
       </c>
       <c r="H65" s="4" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="11" t="n">
         <v>64</v>
       </c>
-      <c r="B66" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="C66" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D66" s="2" t="n">
-        <v>2</v>
+      <c r="B66" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>162</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>125</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>154</v>
+        <v>127</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>127</v>
       </c>
       <c r="H66" s="4" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4329,25 +4389,25 @@
         <v>65</v>
       </c>
       <c r="B67" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="D67" s="2" t="s">
         <v>162</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="D67" s="2" t="n">
-        <v>2</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>125</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>154</v>
+        <v>127</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>127</v>
       </c>
       <c r="H67" s="4" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4358,22 +4418,22 @@
         <v>34</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="E68" s="2" t="n">
-        <v>2</v>
+      <c r="E68" s="2" t="s">
+        <v>162</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>154</v>
+        <v>127</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>127</v>
       </c>
       <c r="H68" s="4" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4381,25 +4441,25 @@
         <v>67</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="E69" s="2" t="n">
-        <v>2</v>
+      <c r="E69" s="2" t="s">
+        <v>162</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>154</v>
+        <v>127</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>127</v>
       </c>
       <c r="H69" s="4" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4407,51 +4467,51 @@
         <v>68</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C70" s="15" t="s">
-        <v>33</v>
+        <v>56</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>57</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>34</v>
+        <v>125</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>35</v>
+        <v>162</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="G70" s="2" t="n">
-        <v>2</v>
+        <v>127</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>127</v>
       </c>
       <c r="H70" s="4" t="s">
-        <v>36</v>
+        <v>167</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="11" t="n">
         <v>69</v>
       </c>
-      <c r="B71" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C71" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="D71" s="2" t="s">
-        <v>164</v>
+      <c r="B71" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D71" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>34</v>
+        <v>125</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>35</v>
+        <v>162</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H71" s="4" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4459,51 +4519,51 @@
         <v>70</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="C72" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="D72" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="H72" s="4" t="s">
         <v>167</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="E72" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F72" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G72" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="H72" s="14" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="11" t="n">
         <v>71</v>
       </c>
-      <c r="B73" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="C73" s="22" t="s">
-        <v>170</v>
+      <c r="B73" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>146</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="E73" s="2" t="s">
-        <v>34</v>
+        <v>125</v>
+      </c>
+      <c r="E73" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>35</v>
+        <v>162</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H73" s="4" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4511,25 +4571,25 @@
         <v>72</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="E74" s="2" t="s">
-        <v>164</v>
+        <v>125</v>
+      </c>
+      <c r="E74" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>34</v>
+        <v>162</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>35</v>
+        <v>127</v>
       </c>
       <c r="H74" s="4" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4537,51 +4597,51 @@
         <v>73</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>177</v>
+        <v>172</v>
+      </c>
+      <c r="C75" s="15" t="s">
+        <v>173</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>174</v>
+        <v>144</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>164</v>
+        <v>35</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="G75" s="2" t="s">
-        <v>35</v>
+        <v>125</v>
+      </c>
+      <c r="G75" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="H75" s="4" t="s">
-        <v>178</v>
+        <v>36</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="11" t="n">
-        <v>75</v>
-      </c>
-      <c r="B76" s="12" t="s">
-        <v>29</v>
+        <v>74</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>155</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>30</v>
+        <v>156</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>174</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>164</v>
+        <v>34</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>35</v>
+        <v>125</v>
       </c>
       <c r="H76" s="4" t="s">
-        <v>128</v>
+        <v>175</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4589,35 +4649,165 @@
         <v>75</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="C77" s="21" t="s">
-        <v>130</v>
+        <v>176</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>177</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>174</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>164</v>
+        <v>34</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="H77" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="H77" s="14" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="11" t="n">
+        <v>71</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C78" s="24" t="s">
+        <v>180</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G78" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="H78" s="4" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="11" t="n">
+        <v>72</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G79" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H79" s="4" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="11" t="n">
+        <v>73</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H80" s="4" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="11" t="n">
+        <v>75</v>
+      </c>
+      <c r="B81" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F81" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G81" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H81" s="4" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="11" t="n">
+        <v>75</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C82" s="23" t="s">
+        <v>130</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G82" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H82" s="4" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="23"/>
-      <c r="B78" s="24"/>
-      <c r="C78" s="25"/>
-      <c r="D78" s="24"/>
-      <c r="E78" s="24"/>
-      <c r="F78" s="24"/>
-      <c r="G78" s="24"/>
+    <row r="83" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="25"/>
+      <c r="B83" s="26"/>
+      <c r="C83" s="27"/>
+      <c r="D83" s="26"/>
+      <c r="E83" s="26"/>
+      <c r="F83" s="26"/>
+      <c r="G83" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -4626,7 +4816,7 @@
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="D1:G1"/>
   </mergeCells>
-  <conditionalFormatting sqref="C1:C2 C4:C724">
+  <conditionalFormatting sqref="C1:C2 C4:C729">
     <cfRule type="containsText" priority="2" operator="containsText" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="uSTO C" dxfId="0">
       <formula>NOT(ISERROR(SEARCH("uSTO C",C1)))</formula>
     </cfRule>
@@ -4637,12 +4827,12 @@
       <formula>NOT(ISERROR(SEARCH("uSTO B",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C2 C4:C733">
+  <conditionalFormatting sqref="C1:C2 C4:C738">
     <cfRule type="containsText" priority="5" operator="containsText" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="uSTO A" dxfId="0">
       <formula>NOT(ISERROR(SEARCH("uSTO A",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C70 C4:C53">
+  <conditionalFormatting sqref="C75 C4:C58">
     <cfRule type="containsText" priority="6" operator="containsText" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="uSTO C" dxfId="0">
       <formula>NOT(ISERROR(SEARCH("uSTO C",C4)))</formula>
     </cfRule>
@@ -4672,23 +4862,23 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:L1048576"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="14.65" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="14.65" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="5" width="18.64"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="5" width="12.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="5" width="16.55"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="5" width="10.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="26" width="10.01"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="9" style="26" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="28" width="10.01"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="9" style="28" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="8"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
     </row>
     <row r="2" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G2" s="5"/>
@@ -4699,67 +4889,67 @@
       <c r="L2" s="5"/>
     </row>
     <row r="3" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="28" t="s">
-        <v>179</v>
-      </c>
-      <c r="B3" s="29" t="s">
-        <v>180</v>
-      </c>
-      <c r="C3" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="D3" s="29" t="s">
-        <v>182</v>
-      </c>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="29"/>
-      <c r="H3" s="29"/>
+      <c r="A3" s="30" t="s">
+        <v>189</v>
+      </c>
+      <c r="B3" s="31" t="s">
+        <v>190</v>
+      </c>
+      <c r="C3" s="31" t="s">
+        <v>191</v>
+      </c>
+      <c r="D3" s="31" t="s">
+        <v>192</v>
+      </c>
+      <c r="E3" s="31"/>
+      <c r="F3" s="31"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="31"/>
       <c r="I3" s="5"/>
     </row>
     <row r="4" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="30" t="s">
-        <v>183</v>
-      </c>
-      <c r="B4" s="31" t="s">
-        <v>184</v>
-      </c>
-      <c r="C4" s="31" t="s">
-        <v>185</v>
-      </c>
-      <c r="D4" s="32" t="n">
+      <c r="A4" s="32" t="s">
+        <v>193</v>
+      </c>
+      <c r="B4" s="33" t="s">
+        <v>194</v>
+      </c>
+      <c r="C4" s="33" t="s">
+        <v>195</v>
+      </c>
+      <c r="D4" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="E4" s="33" t="n">
+      <c r="E4" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="F4" s="33" t="n">
+      <c r="F4" s="35" t="n">
         <v>3</v>
       </c>
-      <c r="G4" s="33" t="n">
+      <c r="G4" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="H4" s="34" t="n">
+      <c r="H4" s="36" t="n">
         <v>1</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="35" t="s">
-        <v>187</v>
-      </c>
-      <c r="B5" s="36" t="s">
-        <v>188</v>
-      </c>
-      <c r="C5" s="36" t="s">
-        <v>189</v>
-      </c>
-      <c r="D5" s="37" t="n">
+      <c r="A5" s="37" t="s">
+        <v>197</v>
+      </c>
+      <c r="B5" s="38" t="s">
+        <v>198</v>
+      </c>
+      <c r="C5" s="38" t="s">
+        <v>199</v>
+      </c>
+      <c r="D5" s="39" t="n">
         <v>9</v>
       </c>
-      <c r="E5" s="38" t="n">
+      <c r="E5" s="40" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="5"/>
@@ -4767,10 +4957,10 @@
       <c r="I5" s="5"/>
     </row>
     <row r="6" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D6" s="39" t="n">
+      <c r="D6" s="41" t="n">
         <v>-2.118</v>
       </c>
-      <c r="E6" s="40" t="n">
+      <c r="E6" s="42" t="n">
         <v>-1.5388</v>
       </c>
       <c r="G6" s="5"/>
@@ -4778,35 +4968,35 @@
       <c r="I6" s="5"/>
     </row>
     <row r="7" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D7" s="39" t="n">
+      <c r="D7" s="41" t="n">
         <v>0.118</v>
       </c>
-      <c r="E7" s="40" t="n">
+      <c r="E7" s="42" t="n">
         <v>0.36327</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D8" s="39" t="n">
+      <c r="D8" s="41" t="n">
         <v>0.118</v>
       </c>
-      <c r="E8" s="40" t="n">
+      <c r="E8" s="42" t="n">
         <v>-0.36327</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D9" s="41" t="n">
+      <c r="D9" s="43" t="n">
         <v>-2.118</v>
       </c>
-      <c r="E9" s="42" t="n">
+      <c r="E9" s="44" t="n">
         <v>1.53884</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D10" s="5" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
     </row>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -4830,375 +5020,375 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B1:D38"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2" min="2" style="43" width="11.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="43" width="14.23"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="4" min="4" style="43" width="11.53"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2" min="2" style="45" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="45" width="14.23"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="4" min="4" style="45" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C1" s="44" t="s">
-        <v>192</v>
-      </c>
-      <c r="D1" s="44"/>
+      <c r="C1" s="46" t="s">
+        <v>202</v>
+      </c>
+      <c r="D1" s="46"/>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="43" t="s">
-        <v>193</v>
-      </c>
-      <c r="C2" s="43" t="s">
-        <v>194</v>
-      </c>
-      <c r="D2" s="43" t="s">
-        <v>195</v>
+      <c r="B2" s="45" t="s">
+        <v>203</v>
+      </c>
+      <c r="C2" s="45" t="s">
+        <v>204</v>
+      </c>
+      <c r="D2" s="45" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="43" t="n">
+      <c r="B3" s="45" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="43" t="n">
+      <c r="C3" s="45" t="n">
         <v>1</v>
       </c>
-      <c r="D3" s="43" t="n">
+      <c r="D3" s="45" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="43" t="n">
+      <c r="B4" s="45" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="43" t="n">
+      <c r="C4" s="45" t="n">
         <v>1</v>
       </c>
-      <c r="D4" s="43" t="n">
+      <c r="D4" s="45" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="43" t="n">
+      <c r="B5" s="45" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="43" t="n">
+      <c r="C5" s="45" t="n">
         <v>1</v>
       </c>
-      <c r="D5" s="43" t="n">
+      <c r="D5" s="45" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="43" t="n">
+      <c r="B6" s="45" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="43" t="n">
+      <c r="C6" s="45" t="n">
         <v>1</v>
       </c>
-      <c r="D6" s="43" t="n">
+      <c r="D6" s="45" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="43" t="n">
+      <c r="B7" s="45" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="43" t="n">
+      <c r="C7" s="45" t="n">
         <v>1</v>
       </c>
-      <c r="D7" s="43" t="n">
+      <c r="D7" s="45" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="43" t="n">
+      <c r="B8" s="45" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="43" t="n">
+      <c r="C8" s="45" t="n">
         <v>1</v>
       </c>
-      <c r="D8" s="43" t="n">
+      <c r="D8" s="45" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="43" t="n">
+      <c r="B9" s="45" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="43" t="n">
+      <c r="C9" s="45" t="n">
         <v>2</v>
       </c>
-      <c r="D9" s="43" t="n">
+      <c r="D9" s="45" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="43" t="n">
+      <c r="B10" s="45" t="n">
         <v>8</v>
       </c>
-      <c r="C10" s="43" t="n">
+      <c r="C10" s="45" t="n">
         <v>2</v>
       </c>
-      <c r="D10" s="43" t="n">
+      <c r="D10" s="45" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="43" t="n">
+      <c r="B11" s="45" t="n">
         <v>9</v>
       </c>
-      <c r="C11" s="43" t="n">
+      <c r="C11" s="45" t="n">
         <v>3</v>
       </c>
-      <c r="D11" s="43" t="n">
+      <c r="D11" s="45" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="43" t="n">
+      <c r="B12" s="45" t="n">
         <v>10</v>
       </c>
-      <c r="C12" s="43" t="n">
+      <c r="C12" s="45" t="n">
         <v>5</v>
       </c>
-      <c r="D12" s="43" t="n">
+      <c r="D12" s="45" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="43" t="n">
+      <c r="B13" s="45" t="n">
         <v>11</v>
       </c>
-      <c r="C13" s="43" t="n">
+      <c r="C13" s="45" t="n">
         <v>6</v>
       </c>
-      <c r="D13" s="43" t="n">
+      <c r="D13" s="45" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="43" t="n">
+      <c r="B14" s="45" t="n">
         <v>12</v>
       </c>
-      <c r="C14" s="43" t="n">
+      <c r="C14" s="45" t="n">
         <v>6</v>
       </c>
-      <c r="D14" s="43" t="n">
+      <c r="D14" s="45" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="43" t="n">
+      <c r="B15" s="45" t="n">
         <v>13</v>
       </c>
-      <c r="C15" s="43" t="n">
+      <c r="C15" s="45" t="n">
         <v>8</v>
       </c>
-      <c r="D15" s="43" t="n">
+      <c r="D15" s="45" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="43" t="n">
+      <c r="B16" s="45" t="n">
         <v>14</v>
       </c>
-      <c r="C16" s="43" t="n">
+      <c r="C16" s="45" t="n">
         <v>9</v>
       </c>
-      <c r="D16" s="43" t="n">
+      <c r="D16" s="45" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="43" t="n">
+      <c r="B17" s="45" t="n">
         <v>15</v>
       </c>
-      <c r="C17" s="43" t="n">
+      <c r="C17" s="45" t="n">
         <v>10</v>
       </c>
-      <c r="D17" s="43" t="n">
+      <c r="D17" s="45" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="43" t="n">
+      <c r="B18" s="45" t="n">
         <v>16</v>
       </c>
-      <c r="C18" s="43" t="n">
+      <c r="C18" s="45" t="n">
         <v>11</v>
       </c>
-      <c r="D18" s="43" t="n">
+      <c r="D18" s="45" t="n">
         <v>11</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="43" t="n">
+      <c r="B19" s="45" t="n">
         <v>17</v>
       </c>
-      <c r="C19" s="43" t="n">
+      <c r="C19" s="45" t="n">
         <v>13</v>
       </c>
-      <c r="D19" s="43" t="n">
+      <c r="D19" s="45" t="n">
         <v>13</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="43" t="n">
+      <c r="B20" s="45" t="n">
         <v>18</v>
       </c>
-      <c r="C20" s="43" t="n">
+      <c r="C20" s="45" t="n">
         <v>14</v>
       </c>
-      <c r="D20" s="43" t="n">
+      <c r="D20" s="45" t="n">
         <v>14</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="43" t="n">
+      <c r="B21" s="45" t="n">
         <v>19</v>
       </c>
-      <c r="C21" s="43" t="n">
+      <c r="C21" s="45" t="n">
         <v>16</v>
       </c>
-      <c r="D21" s="43" t="n">
+      <c r="D21" s="45" t="n">
         <v>16</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="43" t="n">
+      <c r="B22" s="45" t="n">
         <v>20</v>
       </c>
-      <c r="C22" s="43" t="n">
+      <c r="C22" s="45" t="n">
         <v>17</v>
       </c>
-      <c r="D22" s="43" t="n">
+      <c r="D22" s="45" t="n">
         <v>17</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="43" t="n">
+      <c r="B23" s="45" t="n">
         <v>21</v>
       </c>
-      <c r="D23" s="43" t="n">
+      <c r="D23" s="45" t="n">
         <v>20</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="43" t="n">
+      <c r="B24" s="45" t="n">
         <v>22</v>
       </c>
-      <c r="D24" s="43" t="n">
+      <c r="D24" s="45" t="n">
         <v>22</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="43" t="n">
+      <c r="B25" s="45" t="n">
         <v>23</v>
       </c>
-      <c r="D25" s="43" t="n">
+      <c r="D25" s="45" t="n">
         <v>24</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="43" t="n">
+      <c r="B26" s="45" t="n">
         <v>24</v>
       </c>
-      <c r="D26" s="43" t="n">
+      <c r="D26" s="45" t="n">
         <v>25</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="43" t="n">
+      <c r="B27" s="45" t="n">
         <v>25</v>
       </c>
-      <c r="D27" s="43" t="n">
+      <c r="D27" s="45" t="n">
         <v>28</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="43" t="n">
+      <c r="B28" s="45" t="n">
         <v>26</v>
       </c>
-      <c r="D28" s="43" t="n">
+      <c r="D28" s="45" t="n">
         <v>30</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="43" t="n">
+      <c r="B29" s="45" t="n">
         <v>27</v>
       </c>
-      <c r="D29" s="43" t="n">
+      <c r="D29" s="45" t="n">
         <v>33</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="43" t="n">
+      <c r="B30" s="45" t="n">
         <v>28</v>
       </c>
-      <c r="D30" s="43" t="n">
+      <c r="D30" s="45" t="n">
         <v>34</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="43" t="n">
+      <c r="B31" s="45" t="n">
         <v>29</v>
       </c>
-      <c r="D31" s="43" t="n">
+      <c r="D31" s="45" t="n">
         <v>39</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="43" t="n">
+      <c r="B32" s="45" t="n">
         <v>30</v>
       </c>
-      <c r="D32" s="43" t="n">
+      <c r="D32" s="45" t="n">
         <v>40</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="43" t="n">
+      <c r="B33" s="45" t="n">
         <v>31</v>
       </c>
-      <c r="D33" s="43" t="n">
+      <c r="D33" s="45" t="n">
         <v>43</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="43" t="n">
+      <c r="B34" s="45" t="n">
         <v>32</v>
       </c>
-      <c r="D34" s="43" t="n">
+      <c r="D34" s="45" t="n">
         <v>45</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="43" t="n">
+      <c r="B35" s="45" t="n">
         <v>37</v>
       </c>
-      <c r="D35" s="43" t="n">
+      <c r="D35" s="45" t="n">
         <v>62</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="43" t="n">
+      <c r="B36" s="45" t="n">
         <v>42</v>
       </c>
-      <c r="D36" s="43" t="n">
+      <c r="D36" s="45" t="n">
         <v>79</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="43" t="n">
+      <c r="B37" s="45" t="n">
         <v>47</v>
       </c>
-      <c r="D37" s="43" t="n">
+      <c r="D37" s="45" t="n">
         <v>101</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="43" t="n">
+      <c r="B38" s="45" t="n">
         <v>52</v>
       </c>
-      <c r="D38" s="43" t="n">
+      <c r="D38" s="45" t="n">
         <v>119</v>
       </c>
     </row>
